--- a/data/trans_camb/P1435_2011_2023-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1435_2011_2023-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>2,9</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,59</t>
+          <t>0,23; 3,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,19</t>
+          <t>1,66; 7,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,4</t>
+          <t>1,42; 4,58</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>566,77%</t>
+          <t>460,17%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>273,77%</t>
+          <t>232,09%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313,79%</t>
+          <t>268,92%</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,86; 975,98</t>
+          <t>35,37; 906,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,88; 1083,02</t>
+          <t>56,96; 826,01</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,68</t>
+          <t>-0,88; 1,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,06</t>
+          <t>-0,31; 5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,08</t>
+          <t>-0,08; 2,96</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 524,01</t>
+          <t>-77,94; 738,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 212,3</t>
+          <t>-7,49; 166,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 177,7</t>
+          <t>-3,64; 164,22</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>3,77</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,93</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,21</t>
+          <t>0,88; 3,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,92</t>
+          <t>0,2; 6,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,55</t>
+          <t>1,16; 4,8</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>102,99%</t>
+          <t>100,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147,91%</t>
+          <t>153,0%</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 290,34</t>
+          <t>-0,84; 309,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,24; 412,72</t>
+          <t>31,76; 420,07</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,97</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,42</t>
+          <t>-1,86; 0,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 4,53</t>
+          <t>-1,38; 5,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,6</t>
+          <t>-0,74; 2,83</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-52,38%</t>
+          <t>-59,77%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 100,66</t>
+          <t>-17,17; 115,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 103,31</t>
+          <t>-19,11; 109,02</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,55</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,26</t>
+          <t>0,36; 4,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,6</t>
+          <t>-1,1; 6,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,07</t>
+          <t>0,28; 4,53</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115,15%</t>
+          <t>107,05%</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 246,59</t>
+          <t>-15,32; 251,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12,54; 354,32</t>
+          <t>1,55; 338,9</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>4,27</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,31</t>
+          <t>-0,4; 2,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,08</t>
+          <t>4,51; 11,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,04</t>
+          <t>2,28; 6,09</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>240,73%</t>
+          <t>231,96%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>263,68%</t>
+          <t>265,39%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>250,97%</t>
+          <t>254,52%</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>82,91; 738,73</t>
+          <t>74,58; 711,61</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77,9; 682,36</t>
+          <t>75,7; 632,91</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>29,91</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18,48</t>
+          <t>6,13</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,77</t>
+          <t>0,94; 3,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,98; 64,6</t>
+          <t>7,28; 12,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,24; 47,42</t>
+          <t>4,54; 7,73</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>762,2%</t>
+          <t>707,17%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>749,84%</t>
+          <t>245,45%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>843,64%</t>
+          <t>280,08%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>48,21; —</t>
+          <t>45,34; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>178,11; 2318,65</t>
+          <t>131,77; 458,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>225,13; 3160,62</t>
+          <t>149,27; 485,72</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,9</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,65</t>
+          <t>1,19; 3,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,18</t>
+          <t>3,88; 7,73</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,1</t>
+          <t>2,88; 4,94</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>316,0%</t>
+          <t>278,06%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>331,59%</t>
+          <t>365,35%</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>125,71; 636,95</t>
+          <t>115,78; 590,07</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>130,29; 751,64</t>
+          <t>175,22; 752,55</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>3,45</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,9</t>
+          <t>0,91; 1,92</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4,86; 24,8</t>
+          <t>4,37; 6,36</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,0; 17,11</t>
+          <t>2,85; 3,98</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>409,18%</t>
+          <t>425,09%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>289,8%</t>
+          <t>151,26%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>302,16%</t>
+          <t>174,73%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>163,09; 989,44</t>
+          <t>182,39; 1032,7</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>129,51; 814,61</t>
+          <t>109,87; 209,28</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>146,87; 943,83</t>
+          <t>126,28; 232,74</t>
         </is>
       </c>
     </row>
